--- a/docs/Mapping_casi_uso/morte/Morte_017.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_017.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="191">
   <si>
     <t>Sezione</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>testoDataPresuntaMorte</t>
+  </si>
+  <si>
+    <t>Data rinvenimento cadavere</t>
+  </si>
+  <si>
+    <t>dataRinvenimentoCadavere</t>
   </si>
   <si>
     <t>Luogo</t>
@@ -637,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.12890625" customWidth="true" bestFit="true"/>
@@ -1180,19 +1186,19 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>13</v>
@@ -1203,16 +1209,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>65</v>
@@ -1226,16 +1232,16 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>67</v>
@@ -1249,7 +1255,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>68</v>
@@ -1258,7 +1264,7 @@
         <v>31</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>69</v>
@@ -1272,16 +1278,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>71</v>
@@ -1295,16 +1301,16 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>73</v>
@@ -1318,7 +1324,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>74</v>
@@ -1327,7 +1333,7 @@
         <v>31</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>75</v>
@@ -1341,16 +1347,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>77</v>
@@ -1364,7 +1370,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>78</v>
@@ -1373,7 +1379,7 @@
         <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>79</v>
@@ -1387,7 +1393,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>80</v>
@@ -1396,7 +1402,7 @@
         <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>81</v>
@@ -1410,16 +1416,16 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>83</v>
@@ -1433,7 +1439,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>84</v>
@@ -1442,7 +1448,7 @@
         <v>31</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>85</v>
@@ -1456,7 +1462,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>86</v>
@@ -1465,7 +1471,7 @@
         <v>31</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>87</v>
@@ -1479,7 +1485,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>88</v>
@@ -1488,7 +1494,7 @@
         <v>31</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>89</v>
@@ -1502,7 +1508,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>90</v>
@@ -1511,7 +1517,7 @@
         <v>31</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>91</v>
@@ -1525,16 +1531,16 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>93</v>
@@ -1548,7 +1554,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>94</v>
@@ -1557,7 +1563,7 @@
         <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>95</v>
@@ -1571,16 +1577,16 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>97</v>
@@ -1594,7 +1600,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>98</v>
@@ -1603,7 +1609,7 @@
         <v>31</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>99</v>
@@ -1617,7 +1623,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>100</v>
@@ -1626,7 +1632,7 @@
         <v>31</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>101</v>
@@ -1640,7 +1646,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>102</v>
@@ -1649,7 +1655,7 @@
         <v>31</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>103</v>
@@ -1663,7 +1669,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>104</v>
@@ -1672,7 +1678,7 @@
         <v>31</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>105</v>
@@ -1686,7 +1692,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>106</v>
@@ -1695,7 +1701,7 @@
         <v>31</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>107</v>
@@ -1709,7 +1715,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>108</v>
@@ -1718,7 +1724,7 @@
         <v>31</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>109</v>
@@ -1732,7 +1738,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>110</v>
@@ -1741,7 +1747,7 @@
         <v>31</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>111</v>
@@ -1755,7 +1761,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>112</v>
@@ -1764,7 +1770,7 @@
         <v>31</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>113</v>
@@ -1778,7 +1784,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>114</v>
@@ -1787,7 +1793,7 @@
         <v>31</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>115</v>
@@ -1801,7 +1807,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>116</v>
@@ -1810,7 +1816,7 @@
         <v>31</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>117</v>
@@ -1824,7 +1830,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>118</v>
@@ -1833,7 +1839,7 @@
         <v>31</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>119</v>
@@ -1847,19 +1853,19 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>13</v>
@@ -1870,7 +1876,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>123</v>
@@ -1879,7 +1885,7 @@
         <v>10</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>124</v>
@@ -1893,7 +1899,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>125</v>
@@ -1902,7 +1908,7 @@
         <v>10</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>126</v>
@@ -1916,39 +1922,39 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C56" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="F56" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>65</v>
@@ -1957,35 +1963,35 @@
         <v>13</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>70</v>
@@ -1994,7 +2000,7 @@
         <v>31</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>71</v>
@@ -2003,12 +2009,12 @@
         <v>13</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>72</v>
@@ -2017,7 +2023,7 @@
         <v>31</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>73</v>
@@ -2026,12 +2032,12 @@
         <v>13</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>74</v>
@@ -2040,7 +2046,7 @@
         <v>31</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>75</v>
@@ -2049,12 +2055,12 @@
         <v>13</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>76</v>
@@ -2063,7 +2069,7 @@
         <v>31</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>77</v>
@@ -2072,21 +2078,21 @@
         <v>13</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>79</v>
@@ -2095,21 +2101,21 @@
         <v>13</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>81</v>
@@ -2118,21 +2124,21 @@
         <v>13</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>83</v>
@@ -2141,21 +2147,21 @@
         <v>13</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>85</v>
@@ -2164,21 +2170,21 @@
         <v>13</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>87</v>
@@ -2187,21 +2193,21 @@
         <v>13</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>89</v>
@@ -2210,21 +2216,21 @@
         <v>13</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>91</v>
@@ -2233,12 +2239,12 @@
         <v>13</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>92</v>
@@ -2247,7 +2253,7 @@
         <v>31</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>93</v>
@@ -2256,21 +2262,21 @@
         <v>13</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>95</v>
@@ -2279,67 +2285,67 @@
         <v>13</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>99</v>
@@ -2348,21 +2354,21 @@
         <v>13</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>101</v>
@@ -2371,21 +2377,21 @@
         <v>13</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>103</v>
@@ -2394,21 +2400,21 @@
         <v>13</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>105</v>
@@ -2417,21 +2423,21 @@
         <v>13</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>107</v>
@@ -2440,21 +2446,21 @@
         <v>13</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>109</v>
@@ -2463,21 +2469,21 @@
         <v>13</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>111</v>
@@ -2486,35 +2492,35 @@
         <v>13</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>148</v>
@@ -2523,7 +2529,7 @@
         <v>31</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>149</v>
@@ -2532,12 +2538,12 @@
         <v>13</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>150</v>
@@ -2546,7 +2552,7 @@
         <v>31</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>151</v>
@@ -2555,44 +2561,44 @@
         <v>13</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C84" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>65</v>
@@ -2601,35 +2607,35 @@
         <v>13</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>70</v>
@@ -2638,7 +2644,7 @@
         <v>31</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>71</v>
@@ -2647,12 +2653,12 @@
         <v>13</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>72</v>
@@ -2661,7 +2667,7 @@
         <v>31</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>73</v>
@@ -2670,12 +2676,12 @@
         <v>13</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>74</v>
@@ -2684,7 +2690,7 @@
         <v>31</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>75</v>
@@ -2693,12 +2699,12 @@
         <v>13</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>76</v>
@@ -2707,7 +2713,7 @@
         <v>31</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>77</v>
@@ -2716,21 +2722,21 @@
         <v>13</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>79</v>
@@ -2739,21 +2745,21 @@
         <v>13</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>81</v>
@@ -2762,21 +2768,21 @@
         <v>13</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>83</v>
@@ -2785,21 +2791,21 @@
         <v>13</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>85</v>
@@ -2808,21 +2814,21 @@
         <v>13</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>87</v>
@@ -2831,21 +2837,21 @@
         <v>13</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>89</v>
@@ -2854,21 +2860,21 @@
         <v>13</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>91</v>
@@ -2877,12 +2883,12 @@
         <v>13</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>92</v>
@@ -2891,7 +2897,7 @@
         <v>31</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>93</v>
@@ -2900,21 +2906,21 @@
         <v>13</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>95</v>
@@ -2923,67 +2929,67 @@
         <v>13</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>99</v>
@@ -2992,21 +2998,21 @@
         <v>13</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>101</v>
@@ -3015,21 +3021,21 @@
         <v>13</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>103</v>
@@ -3038,21 +3044,21 @@
         <v>13</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>105</v>
@@ -3061,21 +3067,21 @@
         <v>13</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>107</v>
@@ -3084,21 +3090,21 @@
         <v>13</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>109</v>
@@ -3107,21 +3113,21 @@
         <v>13</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>111</v>
@@ -3130,35 +3136,35 @@
         <v>13</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>148</v>
@@ -3167,7 +3173,7 @@
         <v>31</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>149</v>
@@ -3176,12 +3182,12 @@
         <v>13</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>150</v>
@@ -3190,7 +3196,7 @@
         <v>31</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>151</v>
@@ -3199,7 +3205,7 @@
         <v>13</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="112">
@@ -3207,50 +3213,50 @@
         <v>154</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B113" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E113" s="2" t="s">
+      <c r="F113" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>161</v>
@@ -3259,7 +3265,7 @@
         <v>31</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>162</v>
@@ -3268,12 +3274,12 @@
         <v>13</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>163</v>
@@ -3282,7 +3288,7 @@
         <v>31</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>164</v>
@@ -3291,12 +3297,12 @@
         <v>13</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>165</v>
@@ -3305,7 +3311,7 @@
         <v>31</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>166</v>
@@ -3314,12 +3320,12 @@
         <v>13</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>167</v>
@@ -3328,7 +3334,7 @@
         <v>31</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>168</v>
@@ -3337,12 +3343,12 @@
         <v>13</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>169</v>
@@ -3351,44 +3357,44 @@
         <v>31</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>12</v>
+        <v>170</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>172</v>
@@ -3397,44 +3403,44 @@
         <v>31</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>16</v>
+        <v>173</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>175</v>
@@ -3443,7 +3449,7 @@
         <v>31</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>176</v>
@@ -3452,12 +3458,12 @@
         <v>13</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>177</v>
@@ -3466,7 +3472,7 @@
         <v>31</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>178</v>
@@ -3475,12 +3481,12 @@
         <v>13</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>179</v>
@@ -3489,7 +3495,7 @@
         <v>31</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>180</v>
@@ -3498,44 +3504,44 @@
         <v>13</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="F125" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>14</v>
+        <v>160</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D126" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>186</v>
@@ -3549,7 +3555,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>187</v>
@@ -3558,7 +3564,7 @@
         <v>31</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>188</v>
@@ -3567,6 +3573,29 @@
         <v>13</v>
       </c>
       <c r="G127" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G128" s="2" t="s">
         <v>14</v>
       </c>
     </row>
